--- a/inst/models/example_markov/model.xlsx
+++ b/inst/models/example_markov/model.xlsx
@@ -3,25 +3,25 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="settings" sheetId="12" state="visible" r:id="rId10"/>
-    <sheet name="strategies" sheetId="2" state="visible" r:id="rId1"/>
-    <sheet name="groups" sheetId="3" state="visible" r:id="rId2"/>
-    <sheet name="states" sheetId="4" state="visible" r:id="rId3"/>
-    <sheet name="transitions" sheetId="5" state="visible" r:id="rId4"/>
-    <sheet name="values" sheetId="7" state="visible" r:id="rId5"/>
-    <sheet name="summaries" sheetId="8" state="visible" r:id="rId6"/>
-    <sheet name="variables" sheetId="9" state="visible" r:id="rId7"/>
-    <sheet name="multivariate_sampling" sheetId="10" state="visible" r:id="rId8"/>
-    <sheet name="multivariate_sampling_variables" sheetId="11" state="visible" r:id="rId9"/>
+    <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="strategies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="states" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="transitions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="variables" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="summaries" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="multivariate_sampling" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="multivariate_sampling_variables" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t xml:space="preserve">setting</t>
   </si>
@@ -77,22 +77,73 @@
     <t xml:space="preserve">FALSE</t>
   </si>
   <si>
+    <t xml:space="preserve">half_cycle_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discount_timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discount_method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">by_cycle</t>
+  </si>
+  <si>
     <t xml:space="preserve">name</t>
   </si>
   <si>
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
-    <t xml:space="preserve">standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard Care</t>
-  </si>
-  <si>
-    <t xml:space="preserve">new_treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Treatment</t>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abbreviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seritinib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seritinib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cendralimab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cendralimab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low_risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high_risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4</t>
   </si>
   <si>
     <t xml:space="preserve">initial_probability</t>
@@ -101,6 +152,15 @@
     <t xml:space="preserve">state_group</t>
   </si>
   <si>
+    <t xml:space="preserve">share_state_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state_cycle_limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state_cycle_limit_unit</t>
+  </si>
+  <si>
     <t xml:space="preserve">healthy</t>
   </si>
   <si>
@@ -110,12 +170,18 @@
     <t xml:space="preserve">alive</t>
   </si>
   <si>
+    <t xml:space="preserve">cycles</t>
+  </si>
+  <si>
     <t xml:space="preserve">mild</t>
   </si>
   <si>
     <t xml:space="preserve">Mild Disease</t>
   </si>
   <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
     <t xml:space="preserve">severe</t>
   </si>
   <si>
@@ -161,154 +227,220 @@
     <t xml:space="preserve">1 - p_death_severe</t>
   </si>
   <si>
+    <t xml:space="preserve">state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discounting_override</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qaly_healthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u_healthy * cycle_length_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qaly_mild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u_mild * cycle_length_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qaly_severe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u_severe * cycle_length_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost_healthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost_mild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_treatment + c_mild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost_severe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_treatment + c_severe</t>
+  </si>
+  <si>
     <t xml:space="preserve">strategy</t>
   </si>
   <si>
     <t xml:space="preserve">group</t>
   </si>
   <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sampling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background mortality (healthy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.01, sd = 0.002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortality (mild disease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.03, sd = 0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u_healthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility (healthy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u_mild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility (mild disease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u_severe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility (severe disease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.5, sd = 0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_mild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual cost (mild disease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_severe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual cost (severe disease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma(mean = 8000, sd = 1600)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma(mean = 500, sd = 100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma(mean = 3000, sd = 600)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hr_progression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard ratio for progression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lognormal(mean = 0.6, sd = 0.1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Probability of developing mild disease</t>
   </si>
   <si>
+    <t xml:space="preserve">0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.05, sd = 0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.12, sd = 0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_severe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability of progression to severe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.10, sd = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.20, sd = 0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortality (severe disease)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.08</t>
   </si>
   <si>
-    <t xml:space="preserve">p_severe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probability of progression to severe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Background mortality (healthy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortality (mild disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortality (severe disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u_healthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility (healthy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u_mild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility (mild disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u_severe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility (severe disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_mild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual cost (mild disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_severe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual cost (severe disease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hr_progression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hazard ratio for progression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qaly_healthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u_healthy * cycle_length_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qaly_mild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u_mild * cycle_length_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qaly_severe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">u_severe * cycle_length_years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cost_healthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cost_mild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_treatment + c_mild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cost_severe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c_treatment + c_severe</t>
+    <t xml:space="preserve">beta(mean = 0.08, sd = 0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta(mean = 0.18, sd = 0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma(mean = 5000, sd = 1000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lognormal(mean = 0.4, sd = 0.08)</t>
   </si>
   <si>
     <t xml:space="preserve">values</t>
@@ -335,142 +467,34 @@
     <t xml:space="preserve">cost_healthy, cost_mild, cost_severe</t>
   </si>
   <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">low_risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high_risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sampling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.01, sd = 0.002)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.03, sd = 0.005)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvnormal(mean = c(0.8, 2000), sd = c(0.05, 400), cor = -0.3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.5, sd = 0.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma(mean = 8000, sd = 1600)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma(mean = 500, sd = 100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma(mean = 3000, sd = 600)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lognormal(mean = 0.6, sd = 0.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.05, sd = 0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.12, sd = 0.024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.10, sd = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.20, sd = 0.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.08, sd = 0.016)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.18, sd = 0.036)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta(mean = 0.8, sd = 0.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma(mean = 2000, sd = 400)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distribution</t>
+    <t xml:space="preserve">covariance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">size</t>
   </si>
   <si>
     <t xml:space="preserve">cost_utility_correlation</t>
   </si>
   <si>
+    <t xml:space="preserve">mvnormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">Correlated mild utility and cost</t>
   </si>
   <si>
+    <t xml:space="preserve">cost_utility_cov</t>
+  </si>
+  <si>
     <t xml:space="preserve">sampling_name</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">seritinib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seritinib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volantor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volantor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cendralimab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cendralimab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma(mean = 5000, sd = 1000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lognormal(mean = 0.4, sd = 0.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.035</t>
   </si>
 </sst>
 </file>
@@ -801,34 +825,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -844,82 +940,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -935,43 +975,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D2" t="b">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D3" t="b">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -988,72 +1048,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1069,112 +1110,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1190,100 +1251,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1299,43 +1372,161 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>100000</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3"/>
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7"/>
+      <c r="F7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1350,425 +1541,425 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="F1" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="G1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2"/>
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
       <c r="E2"/>
-      <c r="F2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3"/>
+        <v>93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
       <c r="E3"/>
-      <c r="F3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4"/>
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
       <c r="E4"/>
       <c r="F4"/>
-      <c r="G4" t="s">
-        <v>60</v>
-      </c>
+      <c r="G4"/>
       <c r="H4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5"/>
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
       <c r="E5"/>
       <c r="F5"/>
-      <c r="G5" t="s">
-        <v>63</v>
-      </c>
+      <c r="G5"/>
       <c r="H5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6"/>
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
       <c r="E6"/>
-      <c r="F6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7"/>
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
+      </c>
       <c r="E7"/>
       <c r="F7"/>
-      <c r="G7" t="s">
-        <v>69</v>
-      </c>
+      <c r="G7"/>
       <c r="H7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8"/>
+        <v>110</v>
+      </c>
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
       <c r="E8"/>
-      <c r="F8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9" t="s">
-        <v>122</v>
-      </c>
-      <c r="G9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9"/>
+        <v>114</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10"/>
-      <c r="F10" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10"/>
+        <v>116</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11"/>
+        <v>98</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
       <c r="F11"/>
-      <c r="G11" t="s">
-        <v>79</v>
-      </c>
+      <c r="G11"/>
       <c r="H11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12"/>
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13"/>
-      <c r="E13" t="s">
-        <v>106</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13"/>
       <c r="F13" t="s">
-        <v>125</v>
-      </c>
-      <c r="G13" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13"/>
+        <v>35</v>
+      </c>
+      <c r="G13"/>
+      <c r="H13" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14"/>
+      <c r="G14"/>
+      <c r="H14" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15" t="s">
-        <v>106</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="D15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15"/>
       <c r="F15" t="s">
-        <v>127</v>
-      </c>
-      <c r="G15" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15"/>
+        <v>35</v>
+      </c>
+      <c r="G15"/>
+      <c r="H15" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16"/>
-      <c r="E16" t="s">
-        <v>108</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16"/>
       <c r="F16" t="s">
-        <v>128</v>
-      </c>
-      <c r="G16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16"/>
+        <v>38</v>
+      </c>
+      <c r="G16"/>
+      <c r="H16" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17"/>
-      <c r="E17" t="s">
-        <v>106</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17"/>
       <c r="F17" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17"/>
+        <v>35</v>
+      </c>
+      <c r="G17"/>
+      <c r="H17" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18"/>
-      <c r="E18" t="s">
-        <v>108</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D18" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18"/>
       <c r="F18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18"/>
+        <v>38</v>
+      </c>
+      <c r="G18"/>
+      <c r="H18" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19"/>
-      <c r="F19" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19"/>
+        <v>137</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20"/>
-      <c r="F20" t="s">
-        <v>148</v>
-      </c>
-      <c r="G20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20"/>
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20" t="s">
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1783,25 +1974,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1816,45 +2043,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>87</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
